--- a/budget/budget.example.xlsx
+++ b/budget/budget.example.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yellow cells with blue text are inputs. Casa updates C5 each morning from Lunch Money.</t>
+          <t>Yellow cells with blue text are inputs. Butler updates C5 each morning from Lunch Money.</t>
         </is>
       </c>
     </row>
